--- a/ResourcesBD/dsrProfileData.xlsx
+++ b/ResourcesBD/dsrProfileData.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="427">
   <si>
     <t>DT Code*</t>
   </si>
@@ -220,6 +220,1086 @@
   </si>
   <si>
     <t>72453410464651785</t>
+  </si>
+  <si>
+    <t>AUTODSR_A808F</t>
+  </si>
+  <si>
+    <t>03443491200</t>
+  </si>
+  <si>
+    <t>EMP0EB229</t>
+  </si>
+  <si>
+    <t>83815559188130612</t>
+  </si>
+  <si>
+    <t>AUTODSR_AB83F</t>
+  </si>
+  <si>
+    <t>03444420500</t>
+  </si>
+  <si>
+    <t>EMPC460E5</t>
+  </si>
+  <si>
+    <t>18840732216533407</t>
+  </si>
+  <si>
+    <t>AUTODSR_2319E</t>
+  </si>
+  <si>
+    <t>03235602500</t>
+  </si>
+  <si>
+    <t>EMP077A08</t>
+  </si>
+  <si>
+    <t>84858372720354961</t>
+  </si>
+  <si>
+    <t>AUTODSR_98691</t>
+  </si>
+  <si>
+    <t>03237247700</t>
+  </si>
+  <si>
+    <t>EMP4BBD0C</t>
+  </si>
+  <si>
+    <t>89711077114305976</t>
+  </si>
+  <si>
+    <t>AUTODSR_70682</t>
+  </si>
+  <si>
+    <t>03847639900</t>
+  </si>
+  <si>
+    <t>EMPC6C623</t>
+  </si>
+  <si>
+    <t>87062127262636391</t>
+  </si>
+  <si>
+    <t>AUTODSR_04227</t>
+  </si>
+  <si>
+    <t>03848104000</t>
+  </si>
+  <si>
+    <t>EMPA8C28F</t>
+  </si>
+  <si>
+    <t>15398477112124368</t>
+  </si>
+  <si>
+    <t>AUTODSR_4A5E7</t>
+  </si>
+  <si>
+    <t>03608846700</t>
+  </si>
+  <si>
+    <t>EMPDF4B16</t>
+  </si>
+  <si>
+    <t>73010733557081607</t>
+  </si>
+  <si>
+    <t>AUTODSR_FB85C</t>
+  </si>
+  <si>
+    <t>03610981700</t>
+  </si>
+  <si>
+    <t>EMP975E43</t>
+  </si>
+  <si>
+    <t>30315454880024439</t>
+  </si>
+  <si>
+    <t>AUTODSR_26200</t>
+  </si>
+  <si>
+    <t>03005107300</t>
+  </si>
+  <si>
+    <t>EMP1BCB60</t>
+  </si>
+  <si>
+    <t>25745333738733899</t>
+  </si>
+  <si>
+    <t>AUTODSR_5E742</t>
+  </si>
+  <si>
+    <t>03006065200</t>
+  </si>
+  <si>
+    <t>EMP48BEE9</t>
+  </si>
+  <si>
+    <t>55282255100850116</t>
+  </si>
+  <si>
+    <t>AUTODSR_1A234</t>
+  </si>
+  <si>
+    <t>03511130800</t>
+  </si>
+  <si>
+    <t>EMP1B7854</t>
+  </si>
+  <si>
+    <t>69708477749544179</t>
+  </si>
+  <si>
+    <t>AUTODSR_9350A</t>
+  </si>
+  <si>
+    <t>03513221300</t>
+  </si>
+  <si>
+    <t>EMPB88311</t>
+  </si>
+  <si>
+    <t>14625648213190337</t>
+  </si>
+  <si>
+    <t>AUTODSR_7D433</t>
+  </si>
+  <si>
+    <t>03187824400</t>
+  </si>
+  <si>
+    <t>EMP5362B8</t>
+  </si>
+  <si>
+    <t>16522210074967941</t>
+  </si>
+  <si>
+    <t>AUTODSR_DDBBF</t>
+  </si>
+  <si>
+    <t>03189829400</t>
+  </si>
+  <si>
+    <t>EMP9F4BCC</t>
+  </si>
+  <si>
+    <t>87590787947418614</t>
+  </si>
+  <si>
+    <t>AUTODSR_0BF62</t>
+  </si>
+  <si>
+    <t>03170441600</t>
+  </si>
+  <si>
+    <t>EMPC35897</t>
+  </si>
+  <si>
+    <t>27854931043618943</t>
+  </si>
+  <si>
+    <t>AUTODSR_F5FC9</t>
+  </si>
+  <si>
+    <t>03173007700</t>
+  </si>
+  <si>
+    <t>EMP20AE7A</t>
+  </si>
+  <si>
+    <t>46528737603968984</t>
+  </si>
+  <si>
+    <t>AUTODSR_3ECDF</t>
+  </si>
+  <si>
+    <t>03769002700</t>
+  </si>
+  <si>
+    <t>EMPF449C8</t>
+  </si>
+  <si>
+    <t>28632362993590825</t>
+  </si>
+  <si>
+    <t>AUTODSR_1C755</t>
+  </si>
+  <si>
+    <t>03771572900</t>
+  </si>
+  <si>
+    <t>EMPDDA5F6</t>
+  </si>
+  <si>
+    <t>39713324748757023</t>
+  </si>
+  <si>
+    <t>AUTODSR_B7BF3</t>
+  </si>
+  <si>
+    <t>03650748400</t>
+  </si>
+  <si>
+    <t>EMPA23C15</t>
+  </si>
+  <si>
+    <t>96896603165737353</t>
+  </si>
+  <si>
+    <t>AUTODSR_9DAA4</t>
+  </si>
+  <si>
+    <t>03654894300</t>
+  </si>
+  <si>
+    <t>EMP1113AE</t>
+  </si>
+  <si>
+    <t>97204289643572660</t>
+  </si>
+  <si>
+    <t>AUTODSR_A9212</t>
+  </si>
+  <si>
+    <t>03585296200</t>
+  </si>
+  <si>
+    <t>EMPEECDC5</t>
+  </si>
+  <si>
+    <t>24414961953143709</t>
+  </si>
+  <si>
+    <t>AUTODSR_DB2C3</t>
+  </si>
+  <si>
+    <t>03587115400</t>
+  </si>
+  <si>
+    <t>EMPDEA125</t>
+  </si>
+  <si>
+    <t>76791114576263731</t>
+  </si>
+  <si>
+    <t>AUTODSR_CBB4E</t>
+  </si>
+  <si>
+    <t>03745627700</t>
+  </si>
+  <si>
+    <t>EMP27D6C1</t>
+  </si>
+  <si>
+    <t>98887034664980876</t>
+  </si>
+  <si>
+    <t>AUTODSR_3F9D0</t>
+  </si>
+  <si>
+    <t>03747938000</t>
+  </si>
+  <si>
+    <t>EMPA4BA95</t>
+  </si>
+  <si>
+    <t>90200227302667965</t>
+  </si>
+  <si>
+    <t>AUTODSR_994B9</t>
+  </si>
+  <si>
+    <t>03610630000</t>
+  </si>
+  <si>
+    <t>EMPBB2E3B</t>
+  </si>
+  <si>
+    <t>16096949128061632</t>
+  </si>
+  <si>
+    <t>AUTODSR_B7EF7</t>
+  </si>
+  <si>
+    <t>03614389400</t>
+  </si>
+  <si>
+    <t>EMPF318AF</t>
+  </si>
+  <si>
+    <t>56916299142360860</t>
+  </si>
+  <si>
+    <t>AUTODSR_7D58B</t>
+  </si>
+  <si>
+    <t>03889470500</t>
+  </si>
+  <si>
+    <t>EMP4FC233</t>
+  </si>
+  <si>
+    <t>39963920526884916</t>
+  </si>
+  <si>
+    <t>AUTODSR_70723</t>
+  </si>
+  <si>
+    <t>03895410700</t>
+  </si>
+  <si>
+    <t>EMP72036C</t>
+  </si>
+  <si>
+    <t>44190241504818205</t>
+  </si>
+  <si>
+    <t>AUTODSR_52D36</t>
+  </si>
+  <si>
+    <t>03776204500</t>
+  </si>
+  <si>
+    <t>EMP81C4C3</t>
+  </si>
+  <si>
+    <t>62714672387650954</t>
+  </si>
+  <si>
+    <t>AUTODSR_D0133</t>
+  </si>
+  <si>
+    <t>03779182400</t>
+  </si>
+  <si>
+    <t>EMPB8F235</t>
+  </si>
+  <si>
+    <t>57698878536913276</t>
+  </si>
+  <si>
+    <t>AUTODSR_C5631</t>
+  </si>
+  <si>
+    <t>03004053300</t>
+  </si>
+  <si>
+    <t>EMP256A3A</t>
+  </si>
+  <si>
+    <t>19118839020782757</t>
+  </si>
+  <si>
+    <t>AUTODSR_4C864</t>
+  </si>
+  <si>
+    <t>03014218100</t>
+  </si>
+  <si>
+    <t>EMP9A7290</t>
+  </si>
+  <si>
+    <t>13353253201711407</t>
+  </si>
+  <si>
+    <t>AUTODSR_E3931</t>
+  </si>
+  <si>
+    <t>03171372800</t>
+  </si>
+  <si>
+    <t>EMPC2A36B</t>
+  </si>
+  <si>
+    <t>79951440871236858</t>
+  </si>
+  <si>
+    <t>AUTODSR_FDF19</t>
+  </si>
+  <si>
+    <t>03172029800</t>
+  </si>
+  <si>
+    <t>EMP36EF50</t>
+  </si>
+  <si>
+    <t>89624916793343084</t>
+  </si>
+  <si>
+    <t>AUTODSR_F3D7C</t>
+  </si>
+  <si>
+    <t>03707160900</t>
+  </si>
+  <si>
+    <t>EMP1641CD</t>
+  </si>
+  <si>
+    <t>82516123467511386</t>
+  </si>
+  <si>
+    <t>AUTODSR_ACA72</t>
+  </si>
+  <si>
+    <t>03708678500</t>
+  </si>
+  <si>
+    <t>EMPC9CDF0</t>
+  </si>
+  <si>
+    <t>63814373488036586</t>
+  </si>
+  <si>
+    <t>AUTODSR_0C259</t>
+  </si>
+  <si>
+    <t>03827658600</t>
+  </si>
+  <si>
+    <t>EMP734D3E</t>
+  </si>
+  <si>
+    <t>67489384515973650</t>
+  </si>
+  <si>
+    <t>AUTODSR_BFA78</t>
+  </si>
+  <si>
+    <t>03828948300</t>
+  </si>
+  <si>
+    <t>EMP67D580</t>
+  </si>
+  <si>
+    <t>52953439558994749</t>
+  </si>
+  <si>
+    <t>AUTODSR_75C92</t>
+  </si>
+  <si>
+    <t>03943335100</t>
+  </si>
+  <si>
+    <t>EMP7EAC64</t>
+  </si>
+  <si>
+    <t>73669278445936241</t>
+  </si>
+  <si>
+    <t>AUTODSR_B8465</t>
+  </si>
+  <si>
+    <t>03947602800</t>
+  </si>
+  <si>
+    <t>EMP7E6F30</t>
+  </si>
+  <si>
+    <t>22000070845441369</t>
+  </si>
+  <si>
+    <t>AUTODSR_3439B</t>
+  </si>
+  <si>
+    <t>03139531900</t>
+  </si>
+  <si>
+    <t>EMPAF17AE</t>
+  </si>
+  <si>
+    <t>68768216880760102</t>
+  </si>
+  <si>
+    <t>AUTODSR_C8287</t>
+  </si>
+  <si>
+    <t>03144411000</t>
+  </si>
+  <si>
+    <t>EMP5A3275</t>
+  </si>
+  <si>
+    <t>14078768419771155</t>
+  </si>
+  <si>
+    <t>AUTODSR_3EB4E</t>
+  </si>
+  <si>
+    <t>03506848600</t>
+  </si>
+  <si>
+    <t>EMP2B4D60</t>
+  </si>
+  <si>
+    <t>23166432989568787</t>
+  </si>
+  <si>
+    <t>AUTODSR_74194</t>
+  </si>
+  <si>
+    <t>03507445200</t>
+  </si>
+  <si>
+    <t>EMP3C8427</t>
+  </si>
+  <si>
+    <t>43819989817211431</t>
+  </si>
+  <si>
+    <t>AUTODSR_83EE1</t>
+  </si>
+  <si>
+    <t>03428986600</t>
+  </si>
+  <si>
+    <t>EMP85DFF2</t>
+  </si>
+  <si>
+    <t>41186963590308707</t>
+  </si>
+  <si>
+    <t>AUTODSR_9A1DE</t>
+  </si>
+  <si>
+    <t>03429701300</t>
+  </si>
+  <si>
+    <t>EMP57115C</t>
+  </si>
+  <si>
+    <t>23507965895527145</t>
+  </si>
+  <si>
+    <t>AUTODSR_D4D62</t>
+  </si>
+  <si>
+    <t>03855217800</t>
+  </si>
+  <si>
+    <t>EMP8D3CB2</t>
+  </si>
+  <si>
+    <t>53913648099064195</t>
+  </si>
+  <si>
+    <t>AUTODSR_5D9E0</t>
+  </si>
+  <si>
+    <t>03855713100</t>
+  </si>
+  <si>
+    <t>EMPF6E2D9</t>
+  </si>
+  <si>
+    <t>12822680992985912</t>
+  </si>
+  <si>
+    <t>AUTODSR_65629</t>
+  </si>
+  <si>
+    <t>03522397500</t>
+  </si>
+  <si>
+    <t>EMP99DDEF</t>
+  </si>
+  <si>
+    <t>84462049143380676</t>
+  </si>
+  <si>
+    <t>AUTODSR_5063E</t>
+  </si>
+  <si>
+    <t>03523199600</t>
+  </si>
+  <si>
+    <t>EMPFFFFB1</t>
+  </si>
+  <si>
+    <t>72259054383771447</t>
+  </si>
+  <si>
+    <t>AUTODSR_94636</t>
+  </si>
+  <si>
+    <t>03035762400</t>
+  </si>
+  <si>
+    <t>EMP5B6062</t>
+  </si>
+  <si>
+    <t>51782615388697846</t>
+  </si>
+  <si>
+    <t>AUTODSR_926DC</t>
+  </si>
+  <si>
+    <t>03039754400</t>
+  </si>
+  <si>
+    <t>EMP2EFB7B</t>
+  </si>
+  <si>
+    <t>46787255456080835</t>
+  </si>
+  <si>
+    <t>AUTODSR_F7C4A</t>
+  </si>
+  <si>
+    <t>03437723800</t>
+  </si>
+  <si>
+    <t>EMP30DA02</t>
+  </si>
+  <si>
+    <t>93338320910841915</t>
+  </si>
+  <si>
+    <t>AUTODSR_6539C</t>
+  </si>
+  <si>
+    <t>03439432400</t>
+  </si>
+  <si>
+    <t>EMP40777F</t>
+  </si>
+  <si>
+    <t>27334046371541761</t>
+  </si>
+  <si>
+    <t>AUTODSR_3C163</t>
+  </si>
+  <si>
+    <t>03278484900</t>
+  </si>
+  <si>
+    <t>EMP254332</t>
+  </si>
+  <si>
+    <t>56328939457140506</t>
+  </si>
+  <si>
+    <t>AUTODSR_057C7</t>
+  </si>
+  <si>
+    <t>03280450400</t>
+  </si>
+  <si>
+    <t>EMP3B2B15</t>
+  </si>
+  <si>
+    <t>91142033386829220</t>
+  </si>
+  <si>
+    <t>AUTODSR_31EB4</t>
+  </si>
+  <si>
+    <t>03986808300</t>
+  </si>
+  <si>
+    <t>EMP0A48B8</t>
+  </si>
+  <si>
+    <t>70905019071745022</t>
+  </si>
+  <si>
+    <t>AUTODSR_F2BB7</t>
+  </si>
+  <si>
+    <t>03991014200</t>
+  </si>
+  <si>
+    <t>EMPE91163</t>
+  </si>
+  <si>
+    <t>22654600919826691</t>
+  </si>
+  <si>
+    <t>AUTODSR_2FAB6</t>
+  </si>
+  <si>
+    <t>03551288400</t>
+  </si>
+  <si>
+    <t>EMPA4E27F</t>
+  </si>
+  <si>
+    <t>32982845480437707</t>
+  </si>
+  <si>
+    <t>AUTODSR_9AF7E</t>
+  </si>
+  <si>
+    <t>03554535600</t>
+  </si>
+  <si>
+    <t>EMPBE57C2</t>
+  </si>
+  <si>
+    <t>73888536622286176</t>
+  </si>
+  <si>
+    <t>AUTODSR_B9811</t>
+  </si>
+  <si>
+    <t>03580505000</t>
+  </si>
+  <si>
+    <t>EMP7B0C37</t>
+  </si>
+  <si>
+    <t>58093138499967400</t>
+  </si>
+  <si>
+    <t>AUTODSR_8317E</t>
+  </si>
+  <si>
+    <t>03582093700</t>
+  </si>
+  <si>
+    <t>EMP4CE9B4</t>
+  </si>
+  <si>
+    <t>96817341146063432</t>
+  </si>
+  <si>
+    <t>AUTODSR_D6016</t>
+  </si>
+  <si>
+    <t>03529421300</t>
+  </si>
+  <si>
+    <t>EMP2F079A</t>
+  </si>
+  <si>
+    <t>71477253412489155</t>
+  </si>
+  <si>
+    <t>AUTODSR_BA538</t>
+  </si>
+  <si>
+    <t>03532226700</t>
+  </si>
+  <si>
+    <t>EMP020C47</t>
+  </si>
+  <si>
+    <t>26653176585356320</t>
+  </si>
+  <si>
+    <t>AUTODSR_FF752</t>
+  </si>
+  <si>
+    <t>03196921500</t>
+  </si>
+  <si>
+    <t>EMP91A939</t>
+  </si>
+  <si>
+    <t>29933342281848009</t>
+  </si>
+  <si>
+    <t>AUTODSR_C0E55</t>
+  </si>
+  <si>
+    <t>03198711200</t>
+  </si>
+  <si>
+    <t>EMP2308A0</t>
+  </si>
+  <si>
+    <t>39163362212875647</t>
+  </si>
+  <si>
+    <t>AUTODSR_FCEAE</t>
+  </si>
+  <si>
+    <t>03629813200</t>
+  </si>
+  <si>
+    <t>EMP81C7B3</t>
+  </si>
+  <si>
+    <t>23889592603345538</t>
+  </si>
+  <si>
+    <t>AUTODSR_1B15D</t>
+  </si>
+  <si>
+    <t>03632633900</t>
+  </si>
+  <si>
+    <t>EMPD0FAA8</t>
+  </si>
+  <si>
+    <t>19617734903450480</t>
+  </si>
+  <si>
+    <t>AUTODSR_6D50C</t>
+  </si>
+  <si>
+    <t>03747230800</t>
+  </si>
+  <si>
+    <t>EMP2D3EC5</t>
+  </si>
+  <si>
+    <t>27497973739379898</t>
+  </si>
+  <si>
+    <t>AUTODSR_829A5</t>
+  </si>
+  <si>
+    <t>03750344600</t>
+  </si>
+  <si>
+    <t>EMP9571B6</t>
+  </si>
+  <si>
+    <t>17023061303650154</t>
+  </si>
+  <si>
+    <t>AUTODSR_09560</t>
+  </si>
+  <si>
+    <t>03739057500</t>
+  </si>
+  <si>
+    <t>EMPF6C1CE</t>
+  </si>
+  <si>
+    <t>60184311950393834</t>
+  </si>
+  <si>
+    <t>AUTODSR_CBF36</t>
+  </si>
+  <si>
+    <t>03743422000</t>
+  </si>
+  <si>
+    <t>EMP080E8E</t>
+  </si>
+  <si>
+    <t>55424129856366613</t>
+  </si>
+  <si>
+    <t>AUTODSR_5649A</t>
+  </si>
+  <si>
+    <t>03473638900</t>
+  </si>
+  <si>
+    <t>EMP46E724</t>
+  </si>
+  <si>
+    <t>94555869153040126</t>
+  </si>
+  <si>
+    <t>AUTODSR_DB13B</t>
+  </si>
+  <si>
+    <t>03475806100</t>
+  </si>
+  <si>
+    <t>EMP31F2A0</t>
+  </si>
+  <si>
+    <t>12645462902703129</t>
+  </si>
+  <si>
+    <t>AUTODSR_8BA67</t>
+  </si>
+  <si>
+    <t>03337852200</t>
+  </si>
+  <si>
+    <t>EMP698367</t>
+  </si>
+  <si>
+    <t>77873038049747768</t>
+  </si>
+  <si>
+    <t>AUTODSR_A497C</t>
+  </si>
+  <si>
+    <t>03339239500</t>
+  </si>
+  <si>
+    <t>EMPFE8506</t>
+  </si>
+  <si>
+    <t>54574442905206418</t>
+  </si>
+  <si>
+    <t>AUTODSR_CB2F4</t>
+  </si>
+  <si>
+    <t>03017867100</t>
+  </si>
+  <si>
+    <t>EMP94C705</t>
+  </si>
+  <si>
+    <t>77042979612260783</t>
+  </si>
+  <si>
+    <t>AUTODSR_5CAA9</t>
+  </si>
+  <si>
+    <t>03020790200</t>
+  </si>
+  <si>
+    <t>EMPC2C574</t>
+  </si>
+  <si>
+    <t>96675788097414179</t>
+  </si>
+  <si>
+    <t>AUTODSR_BE96F</t>
+  </si>
+  <si>
+    <t>03750869700</t>
+  </si>
+  <si>
+    <t>EMP2400C3</t>
+  </si>
+  <si>
+    <t>32081080702313681</t>
+  </si>
+  <si>
+    <t>AUTODSR_4F227</t>
+  </si>
+  <si>
+    <t>03756644500</t>
+  </si>
+  <si>
+    <t>EMP8240EF</t>
+  </si>
+  <si>
+    <t>13154051678597736</t>
+  </si>
+  <si>
+    <t>AUTODSR_FB72F</t>
+  </si>
+  <si>
+    <t>03557452900</t>
+  </si>
+  <si>
+    <t>EMP91927D</t>
+  </si>
+  <si>
+    <t>85245432637644080</t>
+  </si>
+  <si>
+    <t>AUTODSR_A84D5</t>
+  </si>
+  <si>
+    <t>03558993400</t>
+  </si>
+  <si>
+    <t>EMP8A4FDC</t>
+  </si>
+  <si>
+    <t>97902861866037506</t>
+  </si>
+  <si>
+    <t>AUTODSR_136B7</t>
+  </si>
+  <si>
+    <t>03806878500</t>
+  </si>
+  <si>
+    <t>EMPDCC200</t>
+  </si>
+  <si>
+    <t>88783992569014043</t>
+  </si>
+  <si>
+    <t>AUTODSR_A53E5</t>
+  </si>
+  <si>
+    <t>03808347600</t>
+  </si>
+  <si>
+    <t>EMPD49728</t>
+  </si>
+  <si>
+    <t>53407936350393134</t>
+  </si>
+  <si>
+    <t>AUTODSR_307AB</t>
+  </si>
+  <si>
+    <t>03756460100</t>
+  </si>
+  <si>
+    <t>EMPED61C4</t>
+  </si>
+  <si>
+    <t>91059102931630510</t>
+  </si>
+  <si>
+    <t>AUTODSR_CD068</t>
+  </si>
+  <si>
+    <t>03758382900</t>
+  </si>
+  <si>
+    <t>EMPEDF067</t>
+  </si>
+  <si>
+    <t>11468601987061001</t>
+  </si>
+  <si>
+    <t>AUTODSR_A21B7</t>
+  </si>
+  <si>
+    <t>03399524800</t>
+  </si>
+  <si>
+    <t>EMP1FEA82</t>
+  </si>
+  <si>
+    <t>80094162756662592</t>
+  </si>
+  <si>
+    <t>AUTODSR_B9A60</t>
+  </si>
+  <si>
+    <t>03400771900</t>
+  </si>
+  <si>
+    <t>EMP5EA829</t>
+  </si>
+  <si>
+    <t>83652962292540048</t>
+  </si>
+  <si>
+    <t>AUTODSR_AB694</t>
+  </si>
+  <si>
+    <t>03238957700</t>
+  </si>
+  <si>
+    <t>EMP848C6E</t>
+  </si>
+  <si>
+    <t>63604182356611190</t>
+  </si>
+  <si>
+    <t>AUTODSR_B0A9B</t>
+  </si>
+  <si>
+    <t>03242369000</t>
+  </si>
+  <si>
+    <t>EMP838038</t>
+  </si>
+  <si>
+    <t>82396355373010875</t>
   </si>
 </sst>
 </file>
@@ -649,16 +1729,16 @@
         <v>47</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>59</v>
+        <v>419</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>60</v>
+        <v>420</v>
       </c>
       <c r="E2" t="s" s="0">
         <v>31</v>
       </c>
       <c r="F2" t="s" s="0">
-        <v>61</v>
+        <v>421</v>
       </c>
       <c r="G2" t="s" s="0">
         <v>38</v>
@@ -718,7 +1798,7 @@
         <v>32</v>
       </c>
       <c r="Z2" s="1" t="s">
-        <v>62</v>
+        <v>422</v>
       </c>
       <c r="AA2" t="s" s="0">
         <v>39</v>
@@ -741,16 +1821,16 @@
         <v>53</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>63</v>
+        <v>423</v>
       </c>
       <c r="D3" t="s" s="0">
-        <v>64</v>
+        <v>424</v>
       </c>
       <c r="E3" t="s" s="0">
         <v>35</v>
       </c>
       <c r="F3" t="s" s="0">
-        <v>65</v>
+        <v>425</v>
       </c>
       <c r="G3" t="s" s="0">
         <v>38</v>
@@ -810,7 +1890,7 @@
         <v>32</v>
       </c>
       <c r="Z3" s="1" t="s">
-        <v>66</v>
+        <v>426</v>
       </c>
       <c r="AA3" t="s" s="0">
         <v>45</v>

--- a/ResourcesBD/dsrProfileData.xlsx
+++ b/ResourcesBD/dsrProfileData.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="427">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="506" uniqueCount="475">
   <si>
     <t>DT Code*</t>
   </si>
@@ -1300,6 +1300,150 @@
   </si>
   <si>
     <t>82396355373010875</t>
+  </si>
+  <si>
+    <t>AUTODSR_D376B</t>
+  </si>
+  <si>
+    <t>03108328900</t>
+  </si>
+  <si>
+    <t>EMP1AF690</t>
+  </si>
+  <si>
+    <t>77566103786016338</t>
+  </si>
+  <si>
+    <t>AUTODSR_98B2F</t>
+  </si>
+  <si>
+    <t>03110670100</t>
+  </si>
+  <si>
+    <t>EMPBE1DF2</t>
+  </si>
+  <si>
+    <t>76981728026204524</t>
+  </si>
+  <si>
+    <t>AUTODSR_AD763</t>
+  </si>
+  <si>
+    <t>03610207500</t>
+  </si>
+  <si>
+    <t>EMP08337E</t>
+  </si>
+  <si>
+    <t>88120361979479018</t>
+  </si>
+  <si>
+    <t>AUTODSR_930EC</t>
+  </si>
+  <si>
+    <t>03612206200</t>
+  </si>
+  <si>
+    <t>EMP7F22E7</t>
+  </si>
+  <si>
+    <t>24091941832814544</t>
+  </si>
+  <si>
+    <t>AUTODSR_951B9</t>
+  </si>
+  <si>
+    <t>03350822300</t>
+  </si>
+  <si>
+    <t>EMP30AC2E</t>
+  </si>
+  <si>
+    <t>17463828092898160</t>
+  </si>
+  <si>
+    <t>AUTODSR_DDD9D</t>
+  </si>
+  <si>
+    <t>03354012800</t>
+  </si>
+  <si>
+    <t>EMP9DBC90</t>
+  </si>
+  <si>
+    <t>51709025007592424</t>
+  </si>
+  <si>
+    <t>AUTODSR_34172</t>
+  </si>
+  <si>
+    <t>03514512700</t>
+  </si>
+  <si>
+    <t>EMP58E184</t>
+  </si>
+  <si>
+    <t>91383292294180556</t>
+  </si>
+  <si>
+    <t>AUTODSR_0BAFB</t>
+  </si>
+  <si>
+    <t>03518082800</t>
+  </si>
+  <si>
+    <t>EMP65685A</t>
+  </si>
+  <si>
+    <t>44481968328725630</t>
+  </si>
+  <si>
+    <t>AUTODSR_EDC72</t>
+  </si>
+  <si>
+    <t>03026779100</t>
+  </si>
+  <si>
+    <t>EMPC0991D</t>
+  </si>
+  <si>
+    <t>88474990598050162</t>
+  </si>
+  <si>
+    <t>AUTODSR_69E70</t>
+  </si>
+  <si>
+    <t>03028547300</t>
+  </si>
+  <si>
+    <t>EMPB7E41F</t>
+  </si>
+  <si>
+    <t>50413033627981279</t>
+  </si>
+  <si>
+    <t>AUTODSR_6515E</t>
+  </si>
+  <si>
+    <t>03480688800</t>
+  </si>
+  <si>
+    <t>EMP76EECD</t>
+  </si>
+  <si>
+    <t>28044429117001131</t>
+  </si>
+  <si>
+    <t>AUTODSR_E2D57</t>
+  </si>
+  <si>
+    <t>03481363700</t>
+  </si>
+  <si>
+    <t>EMP258D41</t>
+  </si>
+  <si>
+    <t>20178059326501443</t>
   </si>
 </sst>
 </file>
@@ -1729,16 +1873,16 @@
         <v>47</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>419</v>
+        <v>467</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>420</v>
+        <v>468</v>
       </c>
       <c r="E2" t="s" s="0">
         <v>31</v>
       </c>
       <c r="F2" t="s" s="0">
-        <v>421</v>
+        <v>469</v>
       </c>
       <c r="G2" t="s" s="0">
         <v>38</v>
@@ -1798,7 +1942,7 @@
         <v>32</v>
       </c>
       <c r="Z2" s="1" t="s">
-        <v>422</v>
+        <v>470</v>
       </c>
       <c r="AA2" t="s" s="0">
         <v>39</v>
@@ -1821,16 +1965,16 @@
         <v>53</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>423</v>
+        <v>471</v>
       </c>
       <c r="D3" t="s" s="0">
-        <v>424</v>
+        <v>472</v>
       </c>
       <c r="E3" t="s" s="0">
         <v>35</v>
       </c>
       <c r="F3" t="s" s="0">
-        <v>425</v>
+        <v>473</v>
       </c>
       <c r="G3" t="s" s="0">
         <v>38</v>
@@ -1890,7 +2034,7 @@
         <v>32</v>
       </c>
       <c r="Z3" s="1" t="s">
-        <v>426</v>
+        <v>474</v>
       </c>
       <c r="AA3" t="s" s="0">
         <v>45</v>

--- a/ResourcesBD/dsrProfileData.xlsx
+++ b/ResourcesBD/dsrProfileData.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="506" uniqueCount="475">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="491">
   <si>
     <t>DT Code*</t>
   </si>
@@ -1444,6 +1444,54 @@
   </si>
   <si>
     <t>20178059326501443</t>
+  </si>
+  <si>
+    <t>AUTODSR_68E63</t>
+  </si>
+  <si>
+    <t>03115314900</t>
+  </si>
+  <si>
+    <t>EMP1F9DFB</t>
+  </si>
+  <si>
+    <t>43030222448759162</t>
+  </si>
+  <si>
+    <t>AUTODSR_F6F7B</t>
+  </si>
+  <si>
+    <t>03116663200</t>
+  </si>
+  <si>
+    <t>EMP654880</t>
+  </si>
+  <si>
+    <t>94546049933001596</t>
+  </si>
+  <si>
+    <t>AUTODSR_0A166</t>
+  </si>
+  <si>
+    <t>03028710300</t>
+  </si>
+  <si>
+    <t>EMPA20431</t>
+  </si>
+  <si>
+    <t>28174738280210949</t>
+  </si>
+  <si>
+    <t>AUTODSR_BC801</t>
+  </si>
+  <si>
+    <t>03029509600</t>
+  </si>
+  <si>
+    <t>EMP0322B9</t>
+  </si>
+  <si>
+    <t>19614871700947748</t>
   </si>
 </sst>
 </file>
@@ -1873,16 +1921,16 @@
         <v>47</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>467</v>
+        <v>483</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>468</v>
+        <v>484</v>
       </c>
       <c r="E2" t="s" s="0">
         <v>31</v>
       </c>
       <c r="F2" t="s" s="0">
-        <v>469</v>
+        <v>485</v>
       </c>
       <c r="G2" t="s" s="0">
         <v>38</v>
@@ -1942,7 +1990,7 @@
         <v>32</v>
       </c>
       <c r="Z2" s="1" t="s">
-        <v>470</v>
+        <v>486</v>
       </c>
       <c r="AA2" t="s" s="0">
         <v>39</v>
@@ -1965,16 +2013,16 @@
         <v>53</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>471</v>
+        <v>487</v>
       </c>
       <c r="D3" t="s" s="0">
-        <v>472</v>
+        <v>488</v>
       </c>
       <c r="E3" t="s" s="0">
         <v>35</v>
       </c>
       <c r="F3" t="s" s="0">
-        <v>473</v>
+        <v>489</v>
       </c>
       <c r="G3" t="s" s="0">
         <v>38</v>
@@ -2034,7 +2082,7 @@
         <v>32</v>
       </c>
       <c r="Z3" s="1" t="s">
-        <v>474</v>
+        <v>490</v>
       </c>
       <c r="AA3" t="s" s="0">
         <v>45</v>

--- a/ResourcesBD/dsrProfileData.xlsx
+++ b/ResourcesBD/dsrProfileData.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="491">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="538" uniqueCount="507">
   <si>
     <t>DT Code*</t>
   </si>
@@ -1492,6 +1492,54 @@
   </si>
   <si>
     <t>19614871700947748</t>
+  </si>
+  <si>
+    <t>AUTODSR_F1490</t>
+  </si>
+  <si>
+    <t>03646542900</t>
+  </si>
+  <si>
+    <t>EMPF9F1D7</t>
+  </si>
+  <si>
+    <t>18772892769713091</t>
+  </si>
+  <si>
+    <t>AUTODSR_27037</t>
+  </si>
+  <si>
+    <t>03647232100</t>
+  </si>
+  <si>
+    <t>EMPC23478</t>
+  </si>
+  <si>
+    <t>15306535121895375</t>
+  </si>
+  <si>
+    <t>AUTODSR_C477C</t>
+  </si>
+  <si>
+    <t>03821861200</t>
+  </si>
+  <si>
+    <t>EMP7FC141</t>
+  </si>
+  <si>
+    <t>60921068841831282</t>
+  </si>
+  <si>
+    <t>AUTODSR_A3B03</t>
+  </si>
+  <si>
+    <t>03822514100</t>
+  </si>
+  <si>
+    <t>EMP27038B</t>
+  </si>
+  <si>
+    <t>31302718756031338</t>
   </si>
 </sst>
 </file>
@@ -1921,16 +1969,16 @@
         <v>47</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>483</v>
+        <v>499</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>484</v>
+        <v>500</v>
       </c>
       <c r="E2" t="s" s="0">
         <v>31</v>
       </c>
       <c r="F2" t="s" s="0">
-        <v>485</v>
+        <v>501</v>
       </c>
       <c r="G2" t="s" s="0">
         <v>38</v>
@@ -1990,7 +2038,7 @@
         <v>32</v>
       </c>
       <c r="Z2" s="1" t="s">
-        <v>486</v>
+        <v>502</v>
       </c>
       <c r="AA2" t="s" s="0">
         <v>39</v>
@@ -2013,16 +2061,16 @@
         <v>53</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>487</v>
+        <v>503</v>
       </c>
       <c r="D3" t="s" s="0">
-        <v>488</v>
+        <v>504</v>
       </c>
       <c r="E3" t="s" s="0">
         <v>35</v>
       </c>
       <c r="F3" t="s" s="0">
-        <v>489</v>
+        <v>505</v>
       </c>
       <c r="G3" t="s" s="0">
         <v>38</v>
@@ -2082,7 +2130,7 @@
         <v>32</v>
       </c>
       <c r="Z3" s="1" t="s">
-        <v>490</v>
+        <v>506</v>
       </c>
       <c r="AA3" t="s" s="0">
         <v>45</v>

--- a/ResourcesBD/dsrProfileData.xlsx
+++ b/ResourcesBD/dsrProfileData.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="538" uniqueCount="507">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="554" uniqueCount="523">
   <si>
     <t>DT Code*</t>
   </si>
@@ -1540,6 +1540,54 @@
   </si>
   <si>
     <t>31302718756031338</t>
+  </si>
+  <si>
+    <t>AUTODSR_BAB33</t>
+  </si>
+  <si>
+    <t>03189881800</t>
+  </si>
+  <si>
+    <t>EMP1AB3A6</t>
+  </si>
+  <si>
+    <t>33989030076044418</t>
+  </si>
+  <si>
+    <t>AUTODSR_AD654</t>
+  </si>
+  <si>
+    <t>03191229000</t>
+  </si>
+  <si>
+    <t>EMPC7FC0A</t>
+  </si>
+  <si>
+    <t>38306206557686033</t>
+  </si>
+  <si>
+    <t>AUTODSR_C6082</t>
+  </si>
+  <si>
+    <t>03244069900</t>
+  </si>
+  <si>
+    <t>EMP520D4A</t>
+  </si>
+  <si>
+    <t>28331332355552400</t>
+  </si>
+  <si>
+    <t>AUTODSR_86FC2</t>
+  </si>
+  <si>
+    <t>03246853500</t>
+  </si>
+  <si>
+    <t>EMPCE8C2D</t>
+  </si>
+  <si>
+    <t>25783146291552220</t>
   </si>
 </sst>
 </file>
@@ -1969,16 +2017,16 @@
         <v>47</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>499</v>
+        <v>515</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>500</v>
+        <v>516</v>
       </c>
       <c r="E2" t="s" s="0">
         <v>31</v>
       </c>
       <c r="F2" t="s" s="0">
-        <v>501</v>
+        <v>517</v>
       </c>
       <c r="G2" t="s" s="0">
         <v>38</v>
@@ -2038,7 +2086,7 @@
         <v>32</v>
       </c>
       <c r="Z2" s="1" t="s">
-        <v>502</v>
+        <v>518</v>
       </c>
       <c r="AA2" t="s" s="0">
         <v>39</v>
@@ -2061,16 +2109,16 @@
         <v>53</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>503</v>
+        <v>519</v>
       </c>
       <c r="D3" t="s" s="0">
-        <v>504</v>
+        <v>520</v>
       </c>
       <c r="E3" t="s" s="0">
         <v>35</v>
       </c>
       <c r="F3" t="s" s="0">
-        <v>505</v>
+        <v>521</v>
       </c>
       <c r="G3" t="s" s="0">
         <v>38</v>
@@ -2130,7 +2178,7 @@
         <v>32</v>
       </c>
       <c r="Z3" s="1" t="s">
-        <v>506</v>
+        <v>522</v>
       </c>
       <c r="AA3" t="s" s="0">
         <v>45</v>

--- a/ResourcesBD/dsrProfileData.xlsx
+++ b/ResourcesBD/dsrProfileData.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="554" uniqueCount="523">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="722" uniqueCount="691">
   <si>
     <t>DT Code*</t>
   </si>
@@ -1588,6 +1588,510 @@
   </si>
   <si>
     <t>25783146291552220</t>
+  </si>
+  <si>
+    <t>AUTODSR_A1F70</t>
+  </si>
+  <si>
+    <t>03528137900</t>
+  </si>
+  <si>
+    <t>EMP3CD1AB</t>
+  </si>
+  <si>
+    <t>28141487376379863</t>
+  </si>
+  <si>
+    <t>AUTODSR_7CE61</t>
+  </si>
+  <si>
+    <t>03529020200</t>
+  </si>
+  <si>
+    <t>EMP9E6FDB</t>
+  </si>
+  <si>
+    <t>29265135029364254</t>
+  </si>
+  <si>
+    <t>AUTODSR_56385</t>
+  </si>
+  <si>
+    <t>03721181400</t>
+  </si>
+  <si>
+    <t>EMP9F804B</t>
+  </si>
+  <si>
+    <t>98751361807008320</t>
+  </si>
+  <si>
+    <t>AUTODSR_57989</t>
+  </si>
+  <si>
+    <t>03722408700</t>
+  </si>
+  <si>
+    <t>EMPC3C699</t>
+  </si>
+  <si>
+    <t>67585790869587337</t>
+  </si>
+  <si>
+    <t>AUTODSR_7B288</t>
+  </si>
+  <si>
+    <t>03138724300</t>
+  </si>
+  <si>
+    <t>EMPAF3393</t>
+  </si>
+  <si>
+    <t>88719168619759453</t>
+  </si>
+  <si>
+    <t>AUTODSR_93527</t>
+  </si>
+  <si>
+    <t>03141231400</t>
+  </si>
+  <si>
+    <t>EMPBBE646</t>
+  </si>
+  <si>
+    <t>57992613039156704</t>
+  </si>
+  <si>
+    <t>AUTODSR_70D4A</t>
+  </si>
+  <si>
+    <t>03527106300</t>
+  </si>
+  <si>
+    <t>EMPEDDB1D</t>
+  </si>
+  <si>
+    <t>84642631316547719</t>
+  </si>
+  <si>
+    <t>AUTODSR_F04B1</t>
+  </si>
+  <si>
+    <t>03527868100</t>
+  </si>
+  <si>
+    <t>EMPBC8A53</t>
+  </si>
+  <si>
+    <t>28270567486668065</t>
+  </si>
+  <si>
+    <t>AUTODSR_D14D0</t>
+  </si>
+  <si>
+    <t>03100696900</t>
+  </si>
+  <si>
+    <t>EMPC9DEB7</t>
+  </si>
+  <si>
+    <t>68342118442902380</t>
+  </si>
+  <si>
+    <t>AUTODSR_058E7</t>
+  </si>
+  <si>
+    <t>03101985100</t>
+  </si>
+  <si>
+    <t>EMP0D6669</t>
+  </si>
+  <si>
+    <t>49407593642100638</t>
+  </si>
+  <si>
+    <t>AUTODSR_0FCF9</t>
+  </si>
+  <si>
+    <t>03956093800</t>
+  </si>
+  <si>
+    <t>EMP832B4D</t>
+  </si>
+  <si>
+    <t>46981577845235772</t>
+  </si>
+  <si>
+    <t>AUTODSR_2398A</t>
+  </si>
+  <si>
+    <t>03956780400</t>
+  </si>
+  <si>
+    <t>EMP86F8CF</t>
+  </si>
+  <si>
+    <t>17351400427522186</t>
+  </si>
+  <si>
+    <t>AUTODSR_ADF09</t>
+  </si>
+  <si>
+    <t>03698796000</t>
+  </si>
+  <si>
+    <t>EMPDD1F46</t>
+  </si>
+  <si>
+    <t>43747244386301832</t>
+  </si>
+  <si>
+    <t>AUTODSR_AD075</t>
+  </si>
+  <si>
+    <t>03699823800</t>
+  </si>
+  <si>
+    <t>EMPE3AD4E</t>
+  </si>
+  <si>
+    <t>28143591150936896</t>
+  </si>
+  <si>
+    <t>AUTODSR_DB8D9</t>
+  </si>
+  <si>
+    <t>03527011100</t>
+  </si>
+  <si>
+    <t>EMPBDF5BE</t>
+  </si>
+  <si>
+    <t>83091995835810454</t>
+  </si>
+  <si>
+    <t>AUTODSR_6D9A1</t>
+  </si>
+  <si>
+    <t>03527719100</t>
+  </si>
+  <si>
+    <t>EMP696195</t>
+  </si>
+  <si>
+    <t>46495189896032500</t>
+  </si>
+  <si>
+    <t>AUTODSR_BA31C</t>
+  </si>
+  <si>
+    <t>03957635300</t>
+  </si>
+  <si>
+    <t>EMPC7DC47</t>
+  </si>
+  <si>
+    <t>43606354208685492</t>
+  </si>
+  <si>
+    <t>AUTODSR_24455</t>
+  </si>
+  <si>
+    <t>03958640600</t>
+  </si>
+  <si>
+    <t>EMP62BFF8</t>
+  </si>
+  <si>
+    <t>60055129870698100</t>
+  </si>
+  <si>
+    <t>AUTODSR_A098C</t>
+  </si>
+  <si>
+    <t>03129115300</t>
+  </si>
+  <si>
+    <t>EMPE443EC</t>
+  </si>
+  <si>
+    <t>58876168082010274</t>
+  </si>
+  <si>
+    <t>AUTODSR_12663</t>
+  </si>
+  <si>
+    <t>03129987100</t>
+  </si>
+  <si>
+    <t>EMP1EC62D</t>
+  </si>
+  <si>
+    <t>85249100446802943</t>
+  </si>
+  <si>
+    <t>AUTODSR_A717F</t>
+  </si>
+  <si>
+    <t>03070821700</t>
+  </si>
+  <si>
+    <t>EMP710145</t>
+  </si>
+  <si>
+    <t>79533061517199415</t>
+  </si>
+  <si>
+    <t>AUTODSR_8AE27</t>
+  </si>
+  <si>
+    <t>03072940100</t>
+  </si>
+  <si>
+    <t>EMP6B2C53</t>
+  </si>
+  <si>
+    <t>27439729606519322</t>
+  </si>
+  <si>
+    <t>AUTODSR_7B2C5</t>
+  </si>
+  <si>
+    <t>03356212100</t>
+  </si>
+  <si>
+    <t>EMPB99BE5</t>
+  </si>
+  <si>
+    <t>26844571883466364</t>
+  </si>
+  <si>
+    <t>AUTODSR_CC98C</t>
+  </si>
+  <si>
+    <t>03364301300</t>
+  </si>
+  <si>
+    <t>EMPF6F889</t>
+  </si>
+  <si>
+    <t>92705633334634071</t>
+  </si>
+  <si>
+    <t>AUTODSR_DE291</t>
+  </si>
+  <si>
+    <t>03715788600</t>
+  </si>
+  <si>
+    <t>EMP418CDC</t>
+  </si>
+  <si>
+    <t>92384336273332190</t>
+  </si>
+  <si>
+    <t>AUTODSR_8531C</t>
+  </si>
+  <si>
+    <t>03716259900</t>
+  </si>
+  <si>
+    <t>EMP305D8B</t>
+  </si>
+  <si>
+    <t>24231481305584240</t>
+  </si>
+  <si>
+    <t>AUTODSR_A5678</t>
+  </si>
+  <si>
+    <t>03549009900</t>
+  </si>
+  <si>
+    <t>EMP4EF1F3</t>
+  </si>
+  <si>
+    <t>73913294133879561</t>
+  </si>
+  <si>
+    <t>AUTODSR_A2B88</t>
+  </si>
+  <si>
+    <t>03550886000</t>
+  </si>
+  <si>
+    <t>EMP6F7168</t>
+  </si>
+  <si>
+    <t>98399813688209157</t>
+  </si>
+  <si>
+    <t>AUTODSR_F603C</t>
+  </si>
+  <si>
+    <t>03259095800</t>
+  </si>
+  <si>
+    <t>EMP66B640</t>
+  </si>
+  <si>
+    <t>81120628478612517</t>
+  </si>
+  <si>
+    <t>AUTODSR_06003</t>
+  </si>
+  <si>
+    <t>03260934000</t>
+  </si>
+  <si>
+    <t>EMPD2229E</t>
+  </si>
+  <si>
+    <t>40946236899767650</t>
+  </si>
+  <si>
+    <t>AUTODSR_31ABB</t>
+  </si>
+  <si>
+    <t>03263740200</t>
+  </si>
+  <si>
+    <t>EMP0BC316</t>
+  </si>
+  <si>
+    <t>61244540545116396</t>
+  </si>
+  <si>
+    <t>AUTODSR_2F282</t>
+  </si>
+  <si>
+    <t>03266811600</t>
+  </si>
+  <si>
+    <t>EMP22843C</t>
+  </si>
+  <si>
+    <t>34297830207041697</t>
+  </si>
+  <si>
+    <t>AUTODSR_9FA55</t>
+  </si>
+  <si>
+    <t>03051119800</t>
+  </si>
+  <si>
+    <t>EMP659FB3</t>
+  </si>
+  <si>
+    <t>11468951687711336</t>
+  </si>
+  <si>
+    <t>AUTODSR_F95D0</t>
+  </si>
+  <si>
+    <t>03053503600</t>
+  </si>
+  <si>
+    <t>EMP42A5CE</t>
+  </si>
+  <si>
+    <t>13401431387103597</t>
+  </si>
+  <si>
+    <t>AUTODSR_D7F2E</t>
+  </si>
+  <si>
+    <t>03684509400</t>
+  </si>
+  <si>
+    <t>EMP41CD6D</t>
+  </si>
+  <si>
+    <t>68149954390956008</t>
+  </si>
+  <si>
+    <t>AUTODSR_ECA40</t>
+  </si>
+  <si>
+    <t>03686413200</t>
+  </si>
+  <si>
+    <t>EMP0AEB32</t>
+  </si>
+  <si>
+    <t>87552811269237496</t>
+  </si>
+  <si>
+    <t>AUTODSR_E9016</t>
+  </si>
+  <si>
+    <t>03212217500</t>
+  </si>
+  <si>
+    <t>EMP70D5EB</t>
+  </si>
+  <si>
+    <t>16273686848922480</t>
+  </si>
+  <si>
+    <t>AUTODSR_6A157</t>
+  </si>
+  <si>
+    <t>03212969500</t>
+  </si>
+  <si>
+    <t>EMP027116</t>
+  </si>
+  <si>
+    <t>24061246159487813</t>
+  </si>
+  <si>
+    <t>AUTODSR_617D0</t>
+  </si>
+  <si>
+    <t>03315319900</t>
+  </si>
+  <si>
+    <t>EMP87F5CF</t>
+  </si>
+  <si>
+    <t>34441156673337154</t>
+  </si>
+  <si>
+    <t>AUTODSR_AC893</t>
+  </si>
+  <si>
+    <t>03316018600</t>
+  </si>
+  <si>
+    <t>EMP6C151B</t>
+  </si>
+  <si>
+    <t>17727701443755033</t>
+  </si>
+  <si>
+    <t>AUTODSR_180D3</t>
+  </si>
+  <si>
+    <t>03678713600</t>
+  </si>
+  <si>
+    <t>EMP14AC87</t>
+  </si>
+  <si>
+    <t>27085547507894131</t>
+  </si>
+  <si>
+    <t>AUTODSR_EF503</t>
+  </si>
+  <si>
+    <t>03680645200</t>
+  </si>
+  <si>
+    <t>EMPCCFF55</t>
+  </si>
+  <si>
+    <t>11217422765722257</t>
   </si>
 </sst>
 </file>
@@ -2017,16 +2521,16 @@
         <v>47</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>515</v>
+        <v>683</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>516</v>
+        <v>684</v>
       </c>
       <c r="E2" t="s" s="0">
         <v>31</v>
       </c>
       <c r="F2" t="s" s="0">
-        <v>517</v>
+        <v>685</v>
       </c>
       <c r="G2" t="s" s="0">
         <v>38</v>
@@ -2086,7 +2590,7 @@
         <v>32</v>
       </c>
       <c r="Z2" s="1" t="s">
-        <v>518</v>
+        <v>686</v>
       </c>
       <c r="AA2" t="s" s="0">
         <v>39</v>
@@ -2109,16 +2613,16 @@
         <v>53</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>519</v>
+        <v>687</v>
       </c>
       <c r="D3" t="s" s="0">
-        <v>520</v>
+        <v>688</v>
       </c>
       <c r="E3" t="s" s="0">
         <v>35</v>
       </c>
       <c r="F3" t="s" s="0">
-        <v>521</v>
+        <v>689</v>
       </c>
       <c r="G3" t="s" s="0">
         <v>38</v>
@@ -2178,7 +2682,7 @@
         <v>32</v>
       </c>
       <c r="Z3" s="1" t="s">
-        <v>522</v>
+        <v>690</v>
       </c>
       <c r="AA3" t="s" s="0">
         <v>45</v>

--- a/ResourcesBD/dsrProfileData.xlsx
+++ b/ResourcesBD/dsrProfileData.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="722" uniqueCount="691">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1034" uniqueCount="1003">
   <si>
     <t>DT Code*</t>
   </si>
@@ -2092,6 +2092,942 @@
   </si>
   <si>
     <t>11217422765722257</t>
+  </si>
+  <si>
+    <t>AUTODSR_CE339</t>
+  </si>
+  <si>
+    <t>03507170400</t>
+  </si>
+  <si>
+    <t>EMPC1DB90</t>
+  </si>
+  <si>
+    <t>41740847038671991</t>
+  </si>
+  <si>
+    <t>AUTODSR_09E4E</t>
+  </si>
+  <si>
+    <t>03509203500</t>
+  </si>
+  <si>
+    <t>EMP66F74E</t>
+  </si>
+  <si>
+    <t>41220211961710795</t>
+  </si>
+  <si>
+    <t>AUTODSR_933CD</t>
+  </si>
+  <si>
+    <t>03881308100</t>
+  </si>
+  <si>
+    <t>EMP2E8A6C</t>
+  </si>
+  <si>
+    <t>11713006391821472</t>
+  </si>
+  <si>
+    <t>AUTODSR_F2C80</t>
+  </si>
+  <si>
+    <t>03883283800</t>
+  </si>
+  <si>
+    <t>EMPBCB5CA</t>
+  </si>
+  <si>
+    <t>55618067686072960</t>
+  </si>
+  <si>
+    <t>AUTODSR_F2C9A</t>
+  </si>
+  <si>
+    <t>03452796300</t>
+  </si>
+  <si>
+    <t>EMP419259</t>
+  </si>
+  <si>
+    <t>39071040113914361</t>
+  </si>
+  <si>
+    <t>AUTODSR_1C678</t>
+  </si>
+  <si>
+    <t>03458176800</t>
+  </si>
+  <si>
+    <t>EMP354BEB</t>
+  </si>
+  <si>
+    <t>39620728401934571</t>
+  </si>
+  <si>
+    <t>AUTODSR_ADE6E</t>
+  </si>
+  <si>
+    <t>03678512300</t>
+  </si>
+  <si>
+    <t>EMPADBE43</t>
+  </si>
+  <si>
+    <t>55380301484033140</t>
+  </si>
+  <si>
+    <t>AUTODSR_9CD71</t>
+  </si>
+  <si>
+    <t>03680903300</t>
+  </si>
+  <si>
+    <t>EMP597EF1</t>
+  </si>
+  <si>
+    <t>33703664173102235</t>
+  </si>
+  <si>
+    <t>AUTODSR_EFF1D</t>
+  </si>
+  <si>
+    <t>03178782500</t>
+  </si>
+  <si>
+    <t>EMPA89C8D</t>
+  </si>
+  <si>
+    <t>45232230988115857</t>
+  </si>
+  <si>
+    <t>AUTODSR_BED1A</t>
+  </si>
+  <si>
+    <t>03180830800</t>
+  </si>
+  <si>
+    <t>EMPE9AE89</t>
+  </si>
+  <si>
+    <t>97316392473399581</t>
+  </si>
+  <si>
+    <t>AUTODSR_81931</t>
+  </si>
+  <si>
+    <t>03216239900</t>
+  </si>
+  <si>
+    <t>EMPDACC56</t>
+  </si>
+  <si>
+    <t>33040718314808360</t>
+  </si>
+  <si>
+    <t>AUTODSR_73F9D</t>
+  </si>
+  <si>
+    <t>03219326500</t>
+  </si>
+  <si>
+    <t>EMP035877</t>
+  </si>
+  <si>
+    <t>27699267413635897</t>
+  </si>
+  <si>
+    <t>AUTODSR_58854</t>
+  </si>
+  <si>
+    <t>03561805900</t>
+  </si>
+  <si>
+    <t>EMPBB2360</t>
+  </si>
+  <si>
+    <t>85919838512950808</t>
+  </si>
+  <si>
+    <t>AUTODSR_94EA8</t>
+  </si>
+  <si>
+    <t>03564448800</t>
+  </si>
+  <si>
+    <t>EMPEF1DE9</t>
+  </si>
+  <si>
+    <t>24445668455685456</t>
+  </si>
+  <si>
+    <t>AUTODSR_38492</t>
+  </si>
+  <si>
+    <t>03816150000</t>
+  </si>
+  <si>
+    <t>EMP03B536</t>
+  </si>
+  <si>
+    <t>20335774061712249</t>
+  </si>
+  <si>
+    <t>AUTODSR_D2AC8</t>
+  </si>
+  <si>
+    <t>03818472500</t>
+  </si>
+  <si>
+    <t>EMPFBA244</t>
+  </si>
+  <si>
+    <t>73714956724150423</t>
+  </si>
+  <si>
+    <t>AUTODSR_AF6FD</t>
+  </si>
+  <si>
+    <t>03549972300</t>
+  </si>
+  <si>
+    <t>EMPE72A8A</t>
+  </si>
+  <si>
+    <t>38326185549855329</t>
+  </si>
+  <si>
+    <t>AUTODSR_70F65</t>
+  </si>
+  <si>
+    <t>03552015300</t>
+  </si>
+  <si>
+    <t>EMP1C9649</t>
+  </si>
+  <si>
+    <t>56321372678917316</t>
+  </si>
+  <si>
+    <t>AUTODSR_E5773</t>
+  </si>
+  <si>
+    <t>03094737500</t>
+  </si>
+  <si>
+    <t>EMPF7886B</t>
+  </si>
+  <si>
+    <t>84747786875453012</t>
+  </si>
+  <si>
+    <t>AUTODSR_882ED</t>
+  </si>
+  <si>
+    <t>03096224900</t>
+  </si>
+  <si>
+    <t>EMP1F85E1</t>
+  </si>
+  <si>
+    <t>80522376239064703</t>
+  </si>
+  <si>
+    <t>AUTODSR_31A95</t>
+  </si>
+  <si>
+    <t>03022496300</t>
+  </si>
+  <si>
+    <t>EMP8999F2</t>
+  </si>
+  <si>
+    <t>68203437078330041</t>
+  </si>
+  <si>
+    <t>AUTODSR_01061</t>
+  </si>
+  <si>
+    <t>03024485900</t>
+  </si>
+  <si>
+    <t>EMPFE009C</t>
+  </si>
+  <si>
+    <t>42757508704884567</t>
+  </si>
+  <si>
+    <t>AUTODSR_F6AB1</t>
+  </si>
+  <si>
+    <t>03989421800</t>
+  </si>
+  <si>
+    <t>EMP127800</t>
+  </si>
+  <si>
+    <t>15867373544853546</t>
+  </si>
+  <si>
+    <t>AUTODSR_D3D54</t>
+  </si>
+  <si>
+    <t>03991137300</t>
+  </si>
+  <si>
+    <t>EMP2D9A7F</t>
+  </si>
+  <si>
+    <t>77529076494681426</t>
+  </si>
+  <si>
+    <t>AUTODSR_A9B7F</t>
+  </si>
+  <si>
+    <t>03627164400</t>
+  </si>
+  <si>
+    <t>EMP6150A9</t>
+  </si>
+  <si>
+    <t>71540244252368746</t>
+  </si>
+  <si>
+    <t>AUTODSR_D92E0</t>
+  </si>
+  <si>
+    <t>03628922100</t>
+  </si>
+  <si>
+    <t>EMP67908C</t>
+  </si>
+  <si>
+    <t>43699080966319924</t>
+  </si>
+  <si>
+    <t>AUTODSR_E1E9D</t>
+  </si>
+  <si>
+    <t>03788571300</t>
+  </si>
+  <si>
+    <t>EMP5B7CFA</t>
+  </si>
+  <si>
+    <t>82391298595933597</t>
+  </si>
+  <si>
+    <t>AUTODSR_0D237</t>
+  </si>
+  <si>
+    <t>03790079900</t>
+  </si>
+  <si>
+    <t>EMP5D818A</t>
+  </si>
+  <si>
+    <t>35668738461427285</t>
+  </si>
+  <si>
+    <t>AUTODSR_C52F3</t>
+  </si>
+  <si>
+    <t>03280855900</t>
+  </si>
+  <si>
+    <t>EMPBA98F7</t>
+  </si>
+  <si>
+    <t>78249834474141105</t>
+  </si>
+  <si>
+    <t>AUTODSR_3B479</t>
+  </si>
+  <si>
+    <t>03282805300</t>
+  </si>
+  <si>
+    <t>EMPBA6472</t>
+  </si>
+  <si>
+    <t>54115155727196874</t>
+  </si>
+  <si>
+    <t>AUTODSR_1BFFF</t>
+  </si>
+  <si>
+    <t>03793449900</t>
+  </si>
+  <si>
+    <t>EMPF9C75A</t>
+  </si>
+  <si>
+    <t>65899939824540583</t>
+  </si>
+  <si>
+    <t>AUTODSR_6ED74</t>
+  </si>
+  <si>
+    <t>03795621500</t>
+  </si>
+  <si>
+    <t>EMP65EB2F</t>
+  </si>
+  <si>
+    <t>55395524555114275</t>
+  </si>
+  <si>
+    <t>AUTODSR_044F1</t>
+  </si>
+  <si>
+    <t>03603710600</t>
+  </si>
+  <si>
+    <t>EMP9BF241</t>
+  </si>
+  <si>
+    <t>62625677027458443</t>
+  </si>
+  <si>
+    <t>AUTODSR_66C7B</t>
+  </si>
+  <si>
+    <t>03605636100</t>
+  </si>
+  <si>
+    <t>EMPE18777</t>
+  </si>
+  <si>
+    <t>58466755600012128</t>
+  </si>
+  <si>
+    <t>AUTODSR_AED4C</t>
+  </si>
+  <si>
+    <t>03544274300</t>
+  </si>
+  <si>
+    <t>EMPCADBED</t>
+  </si>
+  <si>
+    <t>56171276994003937</t>
+  </si>
+  <si>
+    <t>AUTODSR_39CC0</t>
+  </si>
+  <si>
+    <t>03547889300</t>
+  </si>
+  <si>
+    <t>EMPC0456F</t>
+  </si>
+  <si>
+    <t>35130178786327608</t>
+  </si>
+  <si>
+    <t>AUTODSR_D953A</t>
+  </si>
+  <si>
+    <t>03110276900</t>
+  </si>
+  <si>
+    <t>EMP3B0EA4</t>
+  </si>
+  <si>
+    <t>93532475272947883</t>
+  </si>
+  <si>
+    <t>AUTODSR_5CC8F</t>
+  </si>
+  <si>
+    <t>03114034200</t>
+  </si>
+  <si>
+    <t>EMP46AF08</t>
+  </si>
+  <si>
+    <t>78264056034403049</t>
+  </si>
+  <si>
+    <t>AUTODSR_223B5</t>
+  </si>
+  <si>
+    <t>03988318700</t>
+  </si>
+  <si>
+    <t>EMPD806B1</t>
+  </si>
+  <si>
+    <t>29965208366461406</t>
+  </si>
+  <si>
+    <t>AUTODSR_4C51C</t>
+  </si>
+  <si>
+    <t>03991591900</t>
+  </si>
+  <si>
+    <t>EMP804E54</t>
+  </si>
+  <si>
+    <t>24806543085044079</t>
+  </si>
+  <si>
+    <t>AUTODSR_A496D</t>
+  </si>
+  <si>
+    <t>03258292700</t>
+  </si>
+  <si>
+    <t>EMP06100B</t>
+  </si>
+  <si>
+    <t>89450771062029877</t>
+  </si>
+  <si>
+    <t>AUTODSR_38A73</t>
+  </si>
+  <si>
+    <t>03260368700</t>
+  </si>
+  <si>
+    <t>EMP35EBC4</t>
+  </si>
+  <si>
+    <t>51532277464537409</t>
+  </si>
+  <si>
+    <t>AUTODSR_6416D</t>
+  </si>
+  <si>
+    <t>03205038900</t>
+  </si>
+  <si>
+    <t>EMP9F3889</t>
+  </si>
+  <si>
+    <t>58138489533789358</t>
+  </si>
+  <si>
+    <t>AUTODSR_681B4</t>
+  </si>
+  <si>
+    <t>03207442700</t>
+  </si>
+  <si>
+    <t>EMPA59449</t>
+  </si>
+  <si>
+    <t>51038305189756563</t>
+  </si>
+  <si>
+    <t>AUTODSR_4B341</t>
+  </si>
+  <si>
+    <t>03388279500</t>
+  </si>
+  <si>
+    <t>EMP81900B</t>
+  </si>
+  <si>
+    <t>17306076928826693</t>
+  </si>
+  <si>
+    <t>AUTODSR_E6AA2</t>
+  </si>
+  <si>
+    <t>03391119300</t>
+  </si>
+  <si>
+    <t>EMPC15256</t>
+  </si>
+  <si>
+    <t>74617822541726985</t>
+  </si>
+  <si>
+    <t>AUTODSR_C5EA6</t>
+  </si>
+  <si>
+    <t>03035479200</t>
+  </si>
+  <si>
+    <t>EMP621D99</t>
+  </si>
+  <si>
+    <t>97895819440659865</t>
+  </si>
+  <si>
+    <t>AUTODSR_0BBEB</t>
+  </si>
+  <si>
+    <t>03041209600</t>
+  </si>
+  <si>
+    <t>EMPD63F9D</t>
+  </si>
+  <si>
+    <t>13406823367665485</t>
+  </si>
+  <si>
+    <t>AUTODSR_8C6B3</t>
+  </si>
+  <si>
+    <t>03995237000</t>
+  </si>
+  <si>
+    <t>EMPADF904</t>
+  </si>
+  <si>
+    <t>54502770290974698</t>
+  </si>
+  <si>
+    <t>AUTODSR_64D97</t>
+  </si>
+  <si>
+    <t>03999945600</t>
+  </si>
+  <si>
+    <t>EMP588F15</t>
+  </si>
+  <si>
+    <t>18906522456700283</t>
+  </si>
+  <si>
+    <t>AUTODSR_7B5FF</t>
+  </si>
+  <si>
+    <t>03916083600</t>
+  </si>
+  <si>
+    <t>EMPFF7F7A</t>
+  </si>
+  <si>
+    <t>99637715436652696</t>
+  </si>
+  <si>
+    <t>AUTODSR_15CC6</t>
+  </si>
+  <si>
+    <t>03920730000</t>
+  </si>
+  <si>
+    <t>EMPC0444F</t>
+  </si>
+  <si>
+    <t>55066420470024892</t>
+  </si>
+  <si>
+    <t>AUTODSR_02217</t>
+  </si>
+  <si>
+    <t>03034468100</t>
+  </si>
+  <si>
+    <t>EMPF88F29</t>
+  </si>
+  <si>
+    <t>71317256419663529</t>
+  </si>
+  <si>
+    <t>AUTODSR_DB605</t>
+  </si>
+  <si>
+    <t>03036475800</t>
+  </si>
+  <si>
+    <t>EMP57C319</t>
+  </si>
+  <si>
+    <t>49232625448751824</t>
+  </si>
+  <si>
+    <t>AUTODSR_E0B18</t>
+  </si>
+  <si>
+    <t>03133550200</t>
+  </si>
+  <si>
+    <t>EMP082CD4</t>
+  </si>
+  <si>
+    <t>85816928209441124</t>
+  </si>
+  <si>
+    <t>AUTODSR_23205</t>
+  </si>
+  <si>
+    <t>03135838800</t>
+  </si>
+  <si>
+    <t>EMPC75139</t>
+  </si>
+  <si>
+    <t>59329528520182759</t>
+  </si>
+  <si>
+    <t>AUTODSR_05BD6</t>
+  </si>
+  <si>
+    <t>03347582000</t>
+  </si>
+  <si>
+    <t>EMP7B662D</t>
+  </si>
+  <si>
+    <t>15913999856382874</t>
+  </si>
+  <si>
+    <t>AUTODSR_68937</t>
+  </si>
+  <si>
+    <t>03350698100</t>
+  </si>
+  <si>
+    <t>EMP6D0938</t>
+  </si>
+  <si>
+    <t>78330794408025849</t>
+  </si>
+  <si>
+    <t>AUTODSR_91CD0</t>
+  </si>
+  <si>
+    <t>03234946900</t>
+  </si>
+  <si>
+    <t>EMPCE38A6</t>
+  </si>
+  <si>
+    <t>21144378291425814</t>
+  </si>
+  <si>
+    <t>AUTODSR_B314B</t>
+  </si>
+  <si>
+    <t>03238339600</t>
+  </si>
+  <si>
+    <t>EMP763049</t>
+  </si>
+  <si>
+    <t>27986748176639651</t>
+  </si>
+  <si>
+    <t>AUTODSR_5ECDB</t>
+  </si>
+  <si>
+    <t>03440774100</t>
+  </si>
+  <si>
+    <t>EMP6676D9</t>
+  </si>
+  <si>
+    <t>78289756910491067</t>
+  </si>
+  <si>
+    <t>AUTODSR_14FFC</t>
+  </si>
+  <si>
+    <t>03442528600</t>
+  </si>
+  <si>
+    <t>EMP54DDDF</t>
+  </si>
+  <si>
+    <t>11836442428299812</t>
+  </si>
+  <si>
+    <t>AUTODSR_7B392</t>
+  </si>
+  <si>
+    <t>03539926200</t>
+  </si>
+  <si>
+    <t>EMPEC6506</t>
+  </si>
+  <si>
+    <t>38571664739213319</t>
+  </si>
+  <si>
+    <t>AUTODSR_1B707</t>
+  </si>
+  <si>
+    <t>03541640600</t>
+  </si>
+  <si>
+    <t>EMP95854E</t>
+  </si>
+  <si>
+    <t>36802661482826421</t>
+  </si>
+  <si>
+    <t>AUTODSR_C72C4</t>
+  </si>
+  <si>
+    <t>03228518100</t>
+  </si>
+  <si>
+    <t>EMP245270</t>
+  </si>
+  <si>
+    <t>78552699980458660</t>
+  </si>
+  <si>
+    <t>AUTODSR_D4494</t>
+  </si>
+  <si>
+    <t>03229796800</t>
+  </si>
+  <si>
+    <t>EMPA75348</t>
+  </si>
+  <si>
+    <t>97256482437062895</t>
+  </si>
+  <si>
+    <t>AUTODSR_7EB06</t>
+  </si>
+  <si>
+    <t>03070063900</t>
+  </si>
+  <si>
+    <t>EMP270031</t>
+  </si>
+  <si>
+    <t>57730090970308678</t>
+  </si>
+  <si>
+    <t>AUTODSR_A3888</t>
+  </si>
+  <si>
+    <t>03071540100</t>
+  </si>
+  <si>
+    <t>EMPCF9C75</t>
+  </si>
+  <si>
+    <t>16574532434395241</t>
+  </si>
+  <si>
+    <t>AUTODSR_EBFD2</t>
+  </si>
+  <si>
+    <t>03862291500</t>
+  </si>
+  <si>
+    <t>EMPEFC0EE</t>
+  </si>
+  <si>
+    <t>58861884621030142</t>
+  </si>
+  <si>
+    <t>AUTODSR_22127</t>
+  </si>
+  <si>
+    <t>03864486600</t>
+  </si>
+  <si>
+    <t>EMP1F0E27</t>
+  </si>
+  <si>
+    <t>48926123812656051</t>
+  </si>
+  <si>
+    <t>AUTODSR_2964D</t>
+  </si>
+  <si>
+    <t>03362559400</t>
+  </si>
+  <si>
+    <t>EMP232EF6</t>
+  </si>
+  <si>
+    <t>20857760716234392</t>
+  </si>
+  <si>
+    <t>AUTODSR_A4FD0</t>
+  </si>
+  <si>
+    <t>03364648300</t>
+  </si>
+  <si>
+    <t>EMPFE6174</t>
+  </si>
+  <si>
+    <t>17105188295609956</t>
+  </si>
+  <si>
+    <t>AUTODSR_824DD</t>
+  </si>
+  <si>
+    <t>03464797200</t>
+  </si>
+  <si>
+    <t>EMP554038</t>
+  </si>
+  <si>
+    <t>60026729121661521</t>
+  </si>
+  <si>
+    <t>AUTODSR_83C05</t>
+  </si>
+  <si>
+    <t>03469023800</t>
+  </si>
+  <si>
+    <t>EMPDC865A</t>
+  </si>
+  <si>
+    <t>80267706221013622</t>
+  </si>
+  <si>
+    <t>AUTODSR_32338</t>
+  </si>
+  <si>
+    <t>03497809000</t>
+  </si>
+  <si>
+    <t>EMP299805</t>
+  </si>
+  <si>
+    <t>69328101981504120</t>
+  </si>
+  <si>
+    <t>AUTODSR_B2EB4</t>
+  </si>
+  <si>
+    <t>03499280900</t>
+  </si>
+  <si>
+    <t>EMPF8AB65</t>
+  </si>
+  <si>
+    <t>90166841292694673</t>
+  </si>
+  <si>
+    <t>AUTODSR_EAD42</t>
+  </si>
+  <si>
+    <t>03831877300</t>
+  </si>
+  <si>
+    <t>EMP2CB7FE</t>
+  </si>
+  <si>
+    <t>39327317234062356</t>
+  </si>
+  <si>
+    <t>AUTODSR_25E5A</t>
+  </si>
+  <si>
+    <t>03833153100</t>
+  </si>
+  <si>
+    <t>EMP733C4C</t>
+  </si>
+  <si>
+    <t>77314904616724853</t>
   </si>
 </sst>
 </file>
@@ -2521,16 +3457,16 @@
         <v>47</v>
       </c>
       <c r="C2" t="s" s="0">
-        <v>683</v>
+        <v>995</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>684</v>
+        <v>996</v>
       </c>
       <c r="E2" t="s" s="0">
         <v>31</v>
       </c>
       <c r="F2" t="s" s="0">
-        <v>685</v>
+        <v>997</v>
       </c>
       <c r="G2" t="s" s="0">
         <v>38</v>
@@ -2590,7 +3526,7 @@
         <v>32</v>
       </c>
       <c r="Z2" s="1" t="s">
-        <v>686</v>
+        <v>998</v>
       </c>
       <c r="AA2" t="s" s="0">
         <v>39</v>
@@ -2613,16 +3549,16 @@
         <v>53</v>
       </c>
       <c r="C3" t="s" s="0">
-        <v>687</v>
+        <v>999</v>
       </c>
       <c r="D3" t="s" s="0">
-        <v>688</v>
+        <v>1000</v>
       </c>
       <c r="E3" t="s" s="0">
         <v>35</v>
       </c>
       <c r="F3" t="s" s="0">
-        <v>689</v>
+        <v>1001</v>
       </c>
       <c r="G3" t="s" s="0">
         <v>38</v>
@@ -2682,7 +3618,7 @@
         <v>32</v>
       </c>
       <c r="Z3" s="1" t="s">
-        <v>690</v>
+        <v>1002</v>
       </c>
       <c r="AA3" t="s" s="0">
         <v>45</v>
